--- a/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_67700_completo.xlsx
+++ b/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_67700_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R901aeb6737ad4158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R36b94004e765451c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.7189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_67700_completo.xlsx
+++ b/134_Cuenca_Camana/_raw_reportes_xlsx/IDConfig_67700_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R36b94004e765451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R530fac5ad520480e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.6968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7675</x:v>
+        <x:v>     30.6968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.7189</x:v>
+        <x:v>     31.6700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.6217</x:v>
+        <x:v>     33.6162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5731</x:v>
+        <x:v>     34.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4758</x:v>
+        <x:v>     36.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.4272</x:v>
+        <x:v>     37.5087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.3786</x:v>
+        <x:v>     38.4818</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.3300</x:v>
+        <x:v>     39.4549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2814</x:v>
+        <x:v>     40.4280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1842</x:v>
+        <x:v>     42.3742</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1356</x:v>
+        <x:v>     43.3474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.0870</x:v>
+        <x:v>     44.3205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0384</x:v>
+        <x:v>     45.2936</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.9898</x:v>
+        <x:v>     46.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.2607</x:v>
+        <x:v>     60.8635</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.0663</x:v>
+        <x:v>     64.7559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9205</x:v>
+        <x:v>     67.6753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.5803</x:v>
+        <x:v>     74.4871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.6775</x:v>
+        <x:v>     72.5409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5316</x:v>
+        <x:v>     75.4602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5524</x:v>
+        <x:v>     55.0248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.2121</x:v>
+        <x:v>     61.8366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.6775</x:v>
+        <x:v>     72.5409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7747</x:v>
+        <x:v>     70.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.6289</x:v>
+        <x:v>     73.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.1149</x:v>
+        <x:v>     63.7828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6982</x:v>
+        <x:v>     52.1054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.7954</x:v>
+        <x:v>     50.1592</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.8926</x:v>
+        <x:v>     48.2130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8440</x:v>
+        <x:v>     49.1861</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7468</x:v>
+        <x:v>     51.1323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.6010</x:v>
+        <x:v>     54.0517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4065</x:v>
+        <x:v>     57.9441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.0663</x:v>
+        <x:v>     64.7559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3372</x:v>
+        <x:v>     79.3527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3372</x:v>
+        <x:v>     79.3527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.6496</x:v>
+        <x:v>     53.0785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.8719</x:v>
+        <x:v>     68.6484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.2886</x:v>
+        <x:v>     80.3258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.9412</x:v>
+        <x:v>     47.2398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.5037</x:v>
+        <x:v>     55.9979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5245</x:v>
+        <x:v>     35.5624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6703</x:v>
+        <x:v>     32.6431</x:v>
       </x:c>
     </x:row>
     <x:row>
